--- a/templates_formats/Notas Momento.xlsx
+++ b/templates_formats/Notas Momento.xlsx
@@ -159,16 +159,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="4"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="9"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="13"/>
@@ -195,23 +191,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="17"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="33"/>
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="27"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="31"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="34"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="38"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -528,623 +515,681 @@
     <col min="11" max="15" width="2.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="C1" s="20" t="s">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A1" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="15"/>
-    </row>
-    <row r="2" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="C2" s="16" t="s">
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A2" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="15"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-    </row>
-    <row r="3" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="C3" s="18" t="s">
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="14"/>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A3" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="15"/>
-    </row>
-    <row r="4" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="C4" s="17" t="s">
+      <c r="B3" s="14"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="14"/>
+      <c r="K3" s="14"/>
+      <c r="L3" s="14"/>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="15"/>
-      <c r="I4" s="14" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="C5" s="19" t="s">
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="15"/>
-      <c r="E5" s="3"/>
-      <c r="G5" s="2"/>
-      <c r="J5" s="2"/>
-    </row>
-    <row r="6" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="D6" s="5" t="s">
+      <c r="B5" s="14"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="14"/>
+      <c r="J5" s="14"/>
+      <c r="K5" s="14"/>
+      <c r="L5" s="14"/>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A6" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="E6" s="3"/>
-      <c r="G6" s="2"/>
-      <c r="I6" s="4"/>
-    </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="14"/>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
         <v>4</v>
       </c>
-      <c r="D7" s="6"/>
+      <c r="D7" s="4"/>
       <c r="E7" s="3"/>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
+      <c r="I7" s="12" t="s">
+        <v>1</v>
+      </c>
       <c r="J7" s="2"/>
     </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
         <v>5</v>
       </c>
-      <c r="D8" s="6"/>
+      <c r="D8" s="4"/>
       <c r="E8" s="3"/>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
     </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="10"/>
+      <c r="D9" s="8"/>
       <c r="E9" s="3"/>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
     </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
         <v>3</v>
       </c>
-      <c r="D10" s="10"/>
+      <c r="D10" s="8"/>
       <c r="E10" s="3"/>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
     </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="D11" s="10" t="s">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="E11" s="3"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-    </row>
-    <row r="12" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="D12" s="6"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="13"/>
+      <c r="J11" s="13"/>
+      <c r="K11" s="13"/>
+      <c r="L11" s="13"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="D12" s="4"/>
       <c r="E12" s="3"/>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
-      <c r="P12" s="9"/>
-    </row>
-    <row r="13" spans="2:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P12" s="7"/>
+    </row>
+    <row r="13" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="E13" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="F13" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="G13" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="H13" s="12" t="s">
+      <c r="H13" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="I13" s="12" t="s">
+      <c r="I13" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="J13" s="12" t="s">
+      <c r="J13" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="K13" s="13"/>
-      <c r="L13" s="13"/>
-      <c r="M13" s="13"/>
-      <c r="N13" s="13"/>
-      <c r="O13" s="13"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="11"/>
+      <c r="O13" s="11"/>
       <c r="P13" s="2"/>
     </row>
-    <row r="14" spans="2:17" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="7">
+    <row r="14" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="5">
         <v>1</v>
       </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
-      <c r="J14" s="8"/>
-      <c r="K14" s="11"/>
-      <c r="L14" s="11"/>
-      <c r="M14" s="11"/>
-      <c r="N14" s="11"/>
-      <c r="O14" s="11"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
+      <c r="K14" s="9"/>
+      <c r="L14" s="9"/>
+      <c r="M14" s="9"/>
+      <c r="N14" s="9"/>
+      <c r="O14" s="9"/>
       <c r="P14" s="2"/>
     </row>
-    <row r="15" spans="2:17" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="7">
+    <row r="15" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="5">
         <v>2</v>
       </c>
-      <c r="C15" s="7"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
-      <c r="K15" s="11"/>
-      <c r="L15" s="11"/>
-      <c r="M15" s="11"/>
-      <c r="N15" s="11"/>
-      <c r="O15" s="11"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6"/>
+      <c r="K15" s="9"/>
+      <c r="L15" s="9"/>
+      <c r="M15" s="9"/>
+      <c r="N15" s="9"/>
+      <c r="O15" s="9"/>
       <c r="P15" s="2"/>
       <c r="Q15" s="2"/>
     </row>
-    <row r="16" spans="2:17" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="7">
+    <row r="16" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="5">
         <v>3</v>
       </c>
-      <c r="C16" s="7"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
-      <c r="J16" s="8"/>
-      <c r="K16" s="11"/>
-      <c r="L16" s="11"/>
-      <c r="M16" s="11"/>
-      <c r="N16" s="11"/>
-      <c r="O16" s="11"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="9"/>
+      <c r="M16" s="9"/>
+      <c r="N16" s="9"/>
+      <c r="O16" s="9"/>
       <c r="P16" s="2"/>
     </row>
-    <row r="17" spans="2:16" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="7">
+    <row r="17" spans="2:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="5">
         <v>4</v>
       </c>
-      <c r="C17" s="7"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
-      <c r="J17" s="8"/>
-      <c r="K17" s="11"/>
-      <c r="L17" s="11"/>
-      <c r="M17" s="11"/>
-      <c r="N17" s="11"/>
-      <c r="O17" s="11"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
+      <c r="K17" s="9"/>
+      <c r="L17" s="9"/>
+      <c r="M17" s="9"/>
+      <c r="N17" s="9"/>
+      <c r="O17" s="9"/>
       <c r="P17" s="2"/>
     </row>
-    <row r="18" spans="2:16" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="7">
+    <row r="18" spans="2:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="5">
         <v>5</v>
       </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="8"/>
-      <c r="I18" s="8"/>
-      <c r="J18" s="8"/>
-      <c r="K18" s="11"/>
-      <c r="L18" s="11"/>
-      <c r="M18" s="11"/>
-      <c r="N18" s="11"/>
-      <c r="O18" s="11"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="6"/>
+      <c r="K18" s="9"/>
+      <c r="L18" s="9"/>
+      <c r="M18" s="9"/>
+      <c r="N18" s="9"/>
+      <c r="O18" s="9"/>
       <c r="P18" s="2"/>
     </row>
-    <row r="19" spans="2:16" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="7">
+    <row r="19" spans="2:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="5">
         <v>6</v>
       </c>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
-      <c r="H19" s="8"/>
-      <c r="I19" s="8"/>
-      <c r="J19" s="8"/>
-      <c r="K19" s="11"/>
-      <c r="L19" s="11"/>
-      <c r="M19" s="11"/>
-      <c r="N19" s="11"/>
-      <c r="O19" s="11"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="6"/>
+      <c r="J19" s="6"/>
+      <c r="K19" s="9"/>
+      <c r="L19" s="9"/>
+      <c r="M19" s="9"/>
+      <c r="N19" s="9"/>
+      <c r="O19" s="9"/>
       <c r="P19" s="2"/>
     </row>
-    <row r="20" spans="2:16" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="7">
+    <row r="20" spans="2:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="5">
         <v>7</v>
       </c>
-      <c r="C20" s="7"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="8"/>
-      <c r="I20" s="8"/>
-      <c r="J20" s="8"/>
-      <c r="K20" s="11"/>
-      <c r="L20" s="11"/>
-      <c r="M20" s="11"/>
-      <c r="N20" s="11"/>
-      <c r="O20" s="11"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="6"/>
+      <c r="J20" s="6"/>
+      <c r="K20" s="9"/>
+      <c r="L20" s="9"/>
+      <c r="M20" s="9"/>
+      <c r="N20" s="9"/>
+      <c r="O20" s="9"/>
       <c r="P20" s="2"/>
     </row>
-    <row r="21" spans="2:16" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="7">
+    <row r="21" spans="2:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="5">
         <v>8</v>
       </c>
-      <c r="C21" s="7"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
-      <c r="G21" s="8"/>
-      <c r="H21" s="8"/>
-      <c r="I21" s="8"/>
-      <c r="J21" s="8"/>
-      <c r="K21" s="11"/>
-      <c r="L21" s="11"/>
-      <c r="M21" s="11"/>
-      <c r="N21" s="11"/>
-      <c r="O21" s="11"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
+      <c r="I21" s="6"/>
+      <c r="J21" s="6"/>
+      <c r="K21" s="9"/>
+      <c r="L21" s="9"/>
+      <c r="M21" s="9"/>
+      <c r="N21" s="9"/>
+      <c r="O21" s="9"/>
       <c r="P21" s="2"/>
     </row>
-    <row r="22" spans="2:16" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="7">
+    <row r="22" spans="2:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="5">
         <v>9</v>
       </c>
-      <c r="C22" s="7"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="8"/>
-      <c r="H22" s="8"/>
-      <c r="I22" s="8"/>
-      <c r="J22" s="8"/>
-      <c r="K22" s="11"/>
-      <c r="L22" s="11"/>
-      <c r="M22" s="11"/>
-      <c r="N22" s="11"/>
-      <c r="O22" s="11"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6"/>
+      <c r="J22" s="6"/>
+      <c r="K22" s="9"/>
+      <c r="L22" s="9"/>
+      <c r="M22" s="9"/>
+      <c r="N22" s="9"/>
+      <c r="O22" s="9"/>
       <c r="P22" s="2"/>
     </row>
-    <row r="23" spans="2:16" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="7">
+    <row r="23" spans="2:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="5">
         <v>10</v>
       </c>
-      <c r="C23" s="7"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
-      <c r="G23" s="8"/>
-      <c r="H23" s="8"/>
-      <c r="I23" s="8"/>
-      <c r="J23" s="8"/>
-      <c r="K23" s="11"/>
-      <c r="L23" s="11"/>
-      <c r="M23" s="11"/>
-      <c r="N23" s="11"/>
-      <c r="O23" s="11"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="6"/>
+      <c r="I23" s="6"/>
+      <c r="J23" s="6"/>
+      <c r="K23" s="9"/>
+      <c r="L23" s="9"/>
+      <c r="M23" s="9"/>
+      <c r="N23" s="9"/>
+      <c r="O23" s="9"/>
       <c r="P23" s="2"/>
     </row>
-    <row r="24" spans="2:16" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="7">
+    <row r="24" spans="2:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="5">
         <v>11</v>
       </c>
-      <c r="C24" s="7"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="8"/>
-      <c r="H24" s="8"/>
-      <c r="I24" s="8"/>
-      <c r="J24" s="8"/>
-      <c r="K24" s="11"/>
-      <c r="L24" s="11"/>
-      <c r="M24" s="11"/>
-      <c r="N24" s="11"/>
-      <c r="O24" s="11"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="6"/>
+      <c r="I24" s="6"/>
+      <c r="J24" s="6"/>
+      <c r="K24" s="9"/>
+      <c r="L24" s="9"/>
+      <c r="M24" s="9"/>
+      <c r="N24" s="9"/>
+      <c r="O24" s="9"/>
       <c r="P24" s="2"/>
     </row>
-    <row r="25" spans="2:16" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="7">
+    <row r="25" spans="2:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="5">
         <v>12</v>
       </c>
-      <c r="C25" s="7"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="8"/>
-      <c r="I25" s="8"/>
-      <c r="J25" s="8"/>
-      <c r="K25" s="11"/>
-      <c r="L25" s="11"/>
-      <c r="M25" s="11"/>
-      <c r="N25" s="11"/>
-      <c r="O25" s="11"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="6"/>
+      <c r="J25" s="6"/>
+      <c r="K25" s="9"/>
+      <c r="L25" s="9"/>
+      <c r="M25" s="9"/>
+      <c r="N25" s="9"/>
+      <c r="O25" s="9"/>
       <c r="P25" s="2"/>
     </row>
-    <row r="26" spans="2:16" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="7">
+    <row r="26" spans="2:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="5">
         <v>13</v>
       </c>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
-      <c r="H26" s="8"/>
-      <c r="I26" s="8"/>
-      <c r="J26" s="8"/>
-      <c r="K26" s="11"/>
-      <c r="L26" s="11"/>
-      <c r="M26" s="11"/>
-      <c r="N26" s="11"/>
-      <c r="O26" s="11"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="6"/>
+      <c r="I26" s="6"/>
+      <c r="J26" s="6"/>
+      <c r="K26" s="9"/>
+      <c r="L26" s="9"/>
+      <c r="M26" s="9"/>
+      <c r="N26" s="9"/>
+      <c r="O26" s="9"/>
       <c r="P26" s="2"/>
     </row>
     <row r="27" spans="2:16" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="11"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="11"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="9"/>
       <c r="H27" s="2"/>
     </row>
     <row r="28" spans="2:16" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="11"/>
-      <c r="C28" s="11"/>
-      <c r="D28" s="11"/>
-      <c r="E28" s="11"/>
-      <c r="F28" s="11"/>
-      <c r="G28" s="11"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="9"/>
       <c r="H28" s="2"/>
     </row>
     <row r="29" spans="2:16" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="11"/>
-      <c r="C29" s="11"/>
-      <c r="D29" s="11"/>
-      <c r="E29" s="11"/>
-      <c r="F29" s="11"/>
-      <c r="G29" s="11"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="9"/>
+      <c r="G29" s="9"/>
       <c r="H29" s="2"/>
     </row>
     <row r="30" spans="2:16" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="11"/>
-      <c r="C30" s="11"/>
-      <c r="D30" s="11"/>
-      <c r="E30" s="11"/>
-      <c r="F30" s="11"/>
-      <c r="G30" s="11"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="9"/>
+      <c r="G30" s="9"/>
       <c r="H30" s="2"/>
     </row>
     <row r="31" spans="2:16" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="11"/>
-      <c r="C31" s="11"/>
-      <c r="D31" s="11"/>
-      <c r="E31" s="11"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="11"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="9"/>
       <c r="H31" s="2"/>
     </row>
     <row r="32" spans="2:16" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="11"/>
-      <c r="C32" s="11"/>
-      <c r="D32" s="11"/>
-      <c r="E32" s="11"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="11"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="9"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="9"/>
+      <c r="G32" s="9"/>
       <c r="H32" s="2"/>
     </row>
     <row r="33" spans="2:9" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="11"/>
-      <c r="C33" s="11"/>
-      <c r="D33" s="11"/>
-      <c r="E33" s="11"/>
-      <c r="F33" s="11"/>
-      <c r="G33" s="11"/>
+      <c r="B33" s="9"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="9"/>
+      <c r="F33" s="9"/>
+      <c r="G33" s="9"/>
       <c r="H33" s="2"/>
     </row>
     <row r="34" spans="2:9" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="11"/>
-      <c r="C34" s="11"/>
-      <c r="D34" s="11"/>
-      <c r="E34" s="11"/>
-      <c r="F34" s="11"/>
-      <c r="G34" s="11"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="9"/>
+      <c r="G34" s="9"/>
       <c r="H34" s="2"/>
     </row>
     <row r="35" spans="2:9" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="11"/>
-      <c r="C35" s="11"/>
-      <c r="D35" s="11"/>
-      <c r="E35" s="11"/>
-      <c r="F35" s="11"/>
-      <c r="G35" s="11"/>
+      <c r="B35" s="9"/>
+      <c r="C35" s="9"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="9"/>
+      <c r="F35" s="9"/>
+      <c r="G35" s="9"/>
       <c r="H35" s="2"/>
     </row>
     <row r="36" spans="2:9" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="11"/>
-      <c r="C36" s="11"/>
-      <c r="D36" s="11"/>
-      <c r="E36" s="11"/>
-      <c r="F36" s="11"/>
-      <c r="G36" s="11"/>
+      <c r="B36" s="9"/>
+      <c r="C36" s="9"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="9"/>
+      <c r="F36" s="9"/>
+      <c r="G36" s="9"/>
       <c r="H36" s="2"/>
     </row>
     <row r="37" spans="2:9" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="11"/>
-      <c r="C37" s="11"/>
-      <c r="D37" s="11"/>
-      <c r="E37" s="11"/>
-      <c r="F37" s="11"/>
-      <c r="G37" s="11"/>
+      <c r="B37" s="9"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="9"/>
+      <c r="G37" s="9"/>
       <c r="H37" s="2"/>
     </row>
     <row r="38" spans="2:9" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="11"/>
-      <c r="C38" s="11"/>
-      <c r="D38" s="11"/>
-      <c r="E38" s="11"/>
-      <c r="F38" s="11"/>
-      <c r="G38" s="11"/>
+      <c r="B38" s="9"/>
+      <c r="C38" s="9"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="9"/>
+      <c r="F38" s="9"/>
+      <c r="G38" s="9"/>
       <c r="H38" s="2"/>
     </row>
     <row r="39" spans="2:9" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="11"/>
-      <c r="C39" s="11"/>
-      <c r="D39" s="11"/>
-      <c r="E39" s="11"/>
-      <c r="F39" s="11"/>
-      <c r="G39" s="11"/>
+      <c r="B39" s="9"/>
+      <c r="C39" s="9"/>
+      <c r="D39" s="9"/>
+      <c r="E39" s="9"/>
+      <c r="F39" s="9"/>
+      <c r="G39" s="9"/>
       <c r="H39" s="2"/>
     </row>
     <row r="40" spans="2:9" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="11"/>
-      <c r="C40" s="11"/>
-      <c r="D40" s="11"/>
-      <c r="E40" s="11"/>
-      <c r="F40" s="11"/>
-      <c r="G40" s="11"/>
+      <c r="B40" s="9"/>
+      <c r="C40" s="9"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="9"/>
+      <c r="F40" s="9"/>
+      <c r="G40" s="9"/>
       <c r="H40" s="2"/>
       <c r="I40" s="2"/>
     </row>
     <row r="41" spans="2:9" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="11"/>
-      <c r="C41" s="11"/>
-      <c r="D41" s="11"/>
-      <c r="E41" s="11"/>
-      <c r="F41" s="11"/>
-      <c r="G41" s="11"/>
+      <c r="B41" s="9"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="9"/>
+      <c r="F41" s="9"/>
+      <c r="G41" s="9"/>
       <c r="H41" s="2"/>
     </row>
     <row r="42" spans="2:9" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="11"/>
-      <c r="C42" s="11"/>
-      <c r="D42" s="11"/>
-      <c r="E42" s="11"/>
-      <c r="F42" s="11"/>
-      <c r="G42" s="11"/>
+      <c r="B42" s="9"/>
+      <c r="C42" s="9"/>
+      <c r="D42" s="9"/>
+      <c r="E42" s="9"/>
+      <c r="F42" s="9"/>
+      <c r="G42" s="9"/>
       <c r="H42" s="2"/>
     </row>
     <row r="43" spans="2:9" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="11"/>
-      <c r="C43" s="11"/>
-      <c r="D43" s="11"/>
-      <c r="E43" s="11"/>
-      <c r="F43" s="11"/>
-      <c r="G43" s="11"/>
+      <c r="B43" s="9"/>
+      <c r="C43" s="9"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="9"/>
+      <c r="F43" s="9"/>
+      <c r="G43" s="9"/>
       <c r="H43" s="2"/>
     </row>
     <row r="44" spans="2:9" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="11"/>
-      <c r="C44" s="11"/>
-      <c r="D44" s="11"/>
-      <c r="E44" s="11"/>
-      <c r="F44" s="11"/>
-      <c r="G44" s="11"/>
+      <c r="B44" s="9"/>
+      <c r="C44" s="9"/>
+      <c r="D44" s="9"/>
+      <c r="E44" s="9"/>
+      <c r="F44" s="9"/>
+      <c r="G44" s="9"/>
       <c r="H44" s="2"/>
     </row>
     <row r="45" spans="2:9" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="11"/>
-      <c r="C45" s="11"/>
-      <c r="D45" s="11"/>
-      <c r="E45" s="11"/>
-      <c r="F45" s="11"/>
-      <c r="G45" s="11"/>
+      <c r="B45" s="9"/>
+      <c r="C45" s="9"/>
+      <c r="D45" s="9"/>
+      <c r="E45" s="9"/>
+      <c r="F45" s="9"/>
+      <c r="G45" s="9"/>
       <c r="H45" s="2"/>
     </row>
     <row r="46" spans="2:9" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="11"/>
-      <c r="C46" s="11"/>
-      <c r="D46" s="11"/>
-      <c r="E46" s="11"/>
-      <c r="F46" s="11"/>
-      <c r="G46" s="11"/>
+      <c r="B46" s="9"/>
+      <c r="C46" s="9"/>
+      <c r="D46" s="9"/>
+      <c r="E46" s="9"/>
+      <c r="F46" s="9"/>
+      <c r="G46" s="9"/>
       <c r="H46" s="2"/>
     </row>
     <row r="47" spans="2:9" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="11"/>
-      <c r="C47" s="11"/>
-      <c r="D47" s="11"/>
-      <c r="E47" s="11"/>
-      <c r="F47" s="11"/>
-      <c r="G47" s="11"/>
+      <c r="B47" s="9"/>
+      <c r="C47" s="9"/>
+      <c r="D47" s="9"/>
+      <c r="E47" s="9"/>
+      <c r="F47" s="9"/>
+      <c r="G47" s="9"/>
       <c r="H47" s="2"/>
     </row>
     <row r="48" spans="2:9" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="11"/>
-      <c r="C48" s="11"/>
-      <c r="D48" s="11"/>
-      <c r="E48" s="11"/>
-      <c r="F48" s="11"/>
-      <c r="G48" s="11"/>
+      <c r="B48" s="9"/>
+      <c r="C48" s="9"/>
+      <c r="D48" s="9"/>
+      <c r="E48" s="9"/>
+      <c r="F48" s="9"/>
+      <c r="G48" s="9"/>
       <c r="H48" s="2"/>
     </row>
     <row r="49" spans="1:16" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="11"/>
-      <c r="C49" s="11"/>
-      <c r="D49" s="11"/>
-      <c r="E49" s="11"/>
-      <c r="F49" s="11"/>
-      <c r="G49" s="11"/>
+      <c r="B49" s="9"/>
+      <c r="C49" s="9"/>
+      <c r="D49" s="9"/>
+      <c r="E49" s="9"/>
+      <c r="F49" s="9"/>
+      <c r="G49" s="9"/>
       <c r="H49" s="2"/>
     </row>
     <row r="50" spans="1:16" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2"/>
-      <c r="J50" s="11"/>
-      <c r="K50" s="11"/>
-      <c r="L50" s="11"/>
-      <c r="M50" s="11"/>
-      <c r="N50" s="11"/>
-      <c r="O50" s="11"/>
+      <c r="J50" s="9"/>
+      <c r="K50" s="9"/>
+      <c r="L50" s="9"/>
+      <c r="M50" s="9"/>
+      <c r="N50" s="9"/>
+      <c r="O50" s="9"/>
       <c r="P50" s="2"/>
     </row>
     <row r="51" spans="1:16" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J51" s="11"/>
-      <c r="K51" s="11"/>
-      <c r="L51" s="11"/>
-      <c r="M51" s="11"/>
-      <c r="N51" s="11"/>
-      <c r="O51" s="11"/>
+      <c r="J51" s="9"/>
+      <c r="K51" s="9"/>
+      <c r="L51" s="9"/>
+      <c r="M51" s="9"/>
+      <c r="N51" s="9"/>
+      <c r="O51" s="9"/>
       <c r="P51" s="2"/>
     </row>
     <row r="52" spans="1:16" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1311,6 +1356,15 @@
       <c r="P69" s="2"/>
     </row>
   </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A11:L11"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A4:L4"/>
+    <mergeCell ref="A5:L5"/>
+    <mergeCell ref="A6:L6"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="172" orientation="landscape" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
 </worksheet>
